--- a/artfynd/A 49509-2025 artfynd.xlsx
+++ b/artfynd/A 49509-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130577576</v>
       </c>
       <c r="B2" t="n">
-        <v>57007</v>
+        <v>57033</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>130577575</v>
       </c>
       <c r="B3" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>130577579</v>
       </c>
       <c r="B4" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49509-2025 artfynd.xlsx
+++ b/artfynd/A 49509-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>130577575</v>
       </c>
       <c r="B3" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>130577579</v>
       </c>
       <c r="B4" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49509-2025 artfynd.xlsx
+++ b/artfynd/A 49509-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>130577575</v>
       </c>
       <c r="B3" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>130577579</v>
       </c>
       <c r="B4" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49509-2025 artfynd.xlsx
+++ b/artfynd/A 49509-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130577576</v>
       </c>
       <c r="B2" t="n">
-        <v>57033</v>
+        <v>57035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>130577575</v>
       </c>
       <c r="B3" t="n">
-        <v>97822</v>
+        <v>97824</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>130577579</v>
       </c>
       <c r="B4" t="n">
-        <v>97822</v>
+        <v>97824</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49509-2025 artfynd.xlsx
+++ b/artfynd/A 49509-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>130577575</v>
       </c>
       <c r="B3" t="n">
-        <v>97824</v>
+        <v>97828</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>130577579</v>
       </c>
       <c r="B4" t="n">
-        <v>97824</v>
+        <v>97828</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49509-2025 artfynd.xlsx
+++ b/artfynd/A 49509-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130577576</v>
       </c>
       <c r="B2" t="n">
-        <v>57035</v>
+        <v>57043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>130577575</v>
       </c>
       <c r="B3" t="n">
-        <v>97828</v>
+        <v>97841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>130577579</v>
       </c>
       <c r="B4" t="n">
-        <v>97828</v>
+        <v>97841</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49509-2025 artfynd.xlsx
+++ b/artfynd/A 49509-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130577576</v>
       </c>
       <c r="B2" t="n">
-        <v>57043</v>
+        <v>57044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>130577575</v>
       </c>
       <c r="B3" t="n">
-        <v>97841</v>
+        <v>97842</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>130577579</v>
       </c>
       <c r="B4" t="n">
-        <v>97841</v>
+        <v>97842</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49509-2025 artfynd.xlsx
+++ b/artfynd/A 49509-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>130577575</v>
       </c>
       <c r="B3" t="n">
-        <v>97842</v>
+        <v>97845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>130577579</v>
       </c>
       <c r="B4" t="n">
-        <v>97842</v>
+        <v>97845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49509-2025 artfynd.xlsx
+++ b/artfynd/A 49509-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>130577575</v>
       </c>
       <c r="B3" t="n">
-        <v>97845</v>
+        <v>97854</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>130577579</v>
       </c>
       <c r="B4" t="n">
-        <v>97845</v>
+        <v>97854</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
